--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -801,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>B25</f>
+        <f>B26</f>
         <v/>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="F8" s="8">
-        <f>B38-(B43+B44+B45)/12</f>
+        <f>B39-(B44+B45+B46)/12</f>
         <v/>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>B36</f>
+        <f>B37</f>
         <v/>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="F9" s="8">
-        <f>B49</f>
+        <f>B50</f>
         <v/>
       </c>
     </row>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>B38</f>
+        <f>B39</f>
         <v/>
       </c>
     </row>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>B49</f>
+        <f>B50</f>
         <v/>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>B54</f>
+        <f>B55</f>
         <v/>
       </c>
     </row>
@@ -1041,393 +1041,410 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Classe énergie (DPE)</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>annoncée par le vendeur — demander le diagnostic complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>HYPOTHÈSES — cellules jaunes à ajuster avec votre conseiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Prix négocié retenu</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>365000</v>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>par défaut le prix affiché — un prix demandé se négocie</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Frais d'acquisition (notaire, garanties)</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>0.08</v>
+          <t>Prix négocié retenu</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>365000</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>par défaut le prix affiché — un prix demandé se négocie</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Frais d'acquisition (notaire, garanties)</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Taux du crédit (hors assurance)</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Durée du crédit (années)</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="n">
-        <v>20</v>
+          <t>Taux du crédit (hors assurance)</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>0.0475</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Taxe foncière (en mois de loyer par an)</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>à remplacer par le montant réel dès que connu</t>
-        </is>
+          <t>Durée du crédit (années)</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Provision entretien &amp; vacance (% du loyer)</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>0.05</v>
+          <t>Taxe foncière (en mois de loyer par an)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>à remplacer par le montant réel dès que connu</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
+          <t>Provision entretien &amp; vacance (% du loyer)</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
           <t>Assurance propriétaire (PNO, €/an)</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B33" s="19" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>PLAN DE FINANCEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Coût d'acquisition total</t>
-        </is>
-      </c>
-      <c r="B35" s="17">
-        <f>B25*(1+B26)</f>
-        <v/>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>prix négocié + frais d'acquisition</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Coût d'acquisition total</t>
         </is>
       </c>
       <c r="B36" s="17">
-        <f>B35*B27</f>
-        <v/>
+        <f>B26*(1+B27)</f>
+        <v/>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>prix négocié + frais d'acquisition</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Montant emprunté</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B37" s="17">
-        <f>B35-B36</f>
+        <f>B36*B28</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Mensualité du crédit</t>
-        </is>
-      </c>
-      <c r="B38" s="23">
-        <f>IFERROR(-PMT(B28/12,B29*12,B37),0)</f>
+          <t>Montant emprunté</t>
+        </is>
+      </c>
+      <c r="B38" s="17">
+        <f>B36-B37</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
+          <t>Mensualité du crédit</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>IFERROR(-PMT(B29/12,B30*12,B38),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
           <t>Service de la dette (annuel)</t>
         </is>
       </c>
-      <c r="B39" s="17">
-        <f>B38*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="B40" s="17">
+        <f>B39*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>EXPLOITATION ANNUELLE</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Loyers annuels HT</t>
-        </is>
-      </c>
-      <c r="B42" s="17">
-        <f>IFERROR(B20*12,0)</f>
-        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>− Taxe foncière</t>
+          <t>Loyers annuels HT</t>
         </is>
       </c>
       <c r="B43" s="17">
-        <f>-IFERROR(B20*B30,0)</f>
+        <f>IFERROR(B20*12,0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>− Entretien &amp; vacance locative</t>
+          <t>− Taxe foncière</t>
         </is>
       </c>
       <c r="B44" s="17">
-        <f>-B42*B31</f>
+        <f>-IFERROR(B20*B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>− Assurance PNO</t>
+          <t>− Entretien &amp; vacance locative</t>
         </is>
       </c>
       <c r="B45" s="17">
-        <f>-B32</f>
+        <f>-B43*B32</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Revenu net avant crédit</t>
+          <t>− Assurance PNO</t>
         </is>
       </c>
       <c r="B46" s="17">
-        <f>B42+B43+B44+B45</f>
+        <f>-B33</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>− Remboursement du crédit</t>
+          <t>Revenu net avant crédit</t>
         </is>
       </c>
       <c r="B47" s="17">
-        <f>-B39</f>
+        <f>B43+B44+B45+B46</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Cash-flow annuel</t>
+          <t>− Remboursement du crédit</t>
         </is>
       </c>
       <c r="B48" s="17">
-        <f>B46-B39</f>
+        <f>-B40</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
+          <t>Cash-flow annuel</t>
+        </is>
+      </c>
+      <c r="B49" s="17">
+        <f>B47-B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
           <t>Cash-flow mensuel</t>
         </is>
       </c>
-      <c r="B49" s="24">
-        <f>B48/12</f>
-        <v/>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="B50" s="24">
+        <f>B49/12</f>
+        <v/>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>positif : le bien se paie tout seul, loyer ≥ crédit + charges</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>LES RATIOS QUE REGARDE LE BANQUIER</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Rendement brut</t>
-        </is>
-      </c>
-      <c r="B52" s="25">
-        <f>IFERROR(B42/B25,"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Rendement net avant crédit</t>
+          <t>Rendement brut</t>
         </is>
       </c>
       <c r="B53" s="25">
-        <f>IFERROR(B46/B35,"")</f>
+        <f>IFERROR(B43/B26,"")</f>
         <v/>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>après taxe foncière, entretien et assurance</t>
+          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>DSCR — couverture de la dette</t>
-        </is>
-      </c>
-      <c r="B54" s="26">
-        <f>IFERROR(B46/B39,"")</f>
+          <t>Rendement net avant crédit</t>
+        </is>
+      </c>
+      <c r="B54" s="25">
+        <f>IFERROR(B47/B36,"")</f>
         <v/>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
+          <t>après taxe foncière, entretien et assurance</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>LTV — part financée par la banque</t>
-        </is>
-      </c>
-      <c r="B55" s="25">
-        <f>IFERROR(B37/B25,"")</f>
+          <t>DSCR — couverture de la dette</t>
+        </is>
+      </c>
+      <c r="B55" s="26">
+        <f>IFERROR(B47/B40,"")</f>
         <v/>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>≤ 80 % est la zone de confort bancaire</t>
+          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Effort d'épargne mensuel si négatif</t>
-        </is>
-      </c>
-      <c r="B56" s="23">
-        <f>MAX(0,-B48/12)</f>
-        <v/>
+          <t>LTV — part financée par la banque</t>
+        </is>
+      </c>
+      <c r="B56" s="25">
+        <f>IFERROR(B38/B26,"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>≤ 80 % est la zone de confort bancaire</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
+          <t>Effort d'épargne mensuel si négatif</t>
+        </is>
+      </c>
+      <c r="B57" s="23">
+        <f>MAX(0,-B49/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
           <t>Score de l'outil de veille</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>64/100</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>rendement, emplacement, prix vs marché, financement, fiscalité</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="27" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>⚠ AVERTISSEMENT : le rendement affiché par le vendeur est anormalement élevé. Exiger le bail et les quittances avant toute offre — ce dossier reprend le loyer annoncé tel quel.</t>
         </is>
       </c>
     </row>
-    <row r="60"/>
+    <row r="61"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A59:C60"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A13:C14"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A60:C61"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B49">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1435,7 +1452,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B50">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1443,7 +1460,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
+  <conditionalFormatting sqref="B55">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.2</formula>
     </cfRule>
@@ -1520,7 +1537,7 @@
         </is>
       </c>
       <c r="G1">
-        <f>'Synthèse'!B29</f>
+        <f>'Synthèse'!B30</f>
         <v/>
       </c>
     </row>
@@ -1529,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$37,"")</f>
+        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$38,"")</f>
         <v/>
       </c>
       <c r="C2" s="8">
@@ -1550,7 +1567,7 @@
         </is>
       </c>
       <c r="G2">
-        <f>'Synthèse'!B28</f>
+        <f>'Synthèse'!B29</f>
         <v/>
       </c>
     </row>
@@ -1575,7 +1592,7 @@
         <v/>
       </c>
       <c r="G3">
-        <f>'Synthèse'!B39</f>
+        <f>'Synthèse'!B40</f>
         <v/>
       </c>
     </row>
@@ -2326,7 +2343,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>Idéalement situé dans le 16eme arrondissement de Paris, ce local commercial bénéficie d’un environnement recherché, caractérisé par son calme, son élégance et son architecture remarquable. Ce secteur prisé, bien desservi par les transports en commun, offre un cadre de vie agréable et dynamique, parfait pour une activité commerciale. Caractéristiques du bien : - Surface commerciale en rez-de-chaussée avec une belle vitrine offrant une visibilité optimale (18,44 m2). - Studio et/ou bureau au 1er étage, idéal pour un usage privé ou un bureau (18,69 m2). - Zone de stockage en sous-sol, chauffée et</t>
+          <t>Idéalement situé dans le 16eme arrondissement de Paris, ce local commercial bénéficie d’un environnement recherché, caractérisé par son calme, son élégance et son architecture remarquable. Ce secteur prisé, bien desservi par les transports en commun, offre un cadre de vie agréable et dynamique, parfait pour une activité commerciale. Caractéristiques du bien : - Surface commerciale en rez-de-chaussée avec une belle vitrine offrant une visibilité optimale (18,44 m2). - Studio et/ou bureau au 1er étage, idéal pour un usage privé ou un bureau (18,69 m2). - Zone de stockage en sous-sol, chauffée et parfaitement exploitable (13,7 m2). Deux escaliers desservent les trois niveaux, facilitant la circulation et l’aménagement des espaces. Ce bien rare sur le marché combine une localisation stratégique et un agencement fonctionnel, parfait pour toute activité nécessitant un espace de vente, un bureau indépendant et une zone de stockage efficace. Les honoraires sont à la charge de l'acquéreur. DPE C - GES B. Bien soumis au régime de la copropriété. Charges annuelles de 1228€. Pas de procédure en cours. Contactez Maxime Ramond Bluzet pour plus d’informations ou organiser une visite : / REF MR-6892-2 Honoraires inclus de 4.29% à la charge de l'acquéreur. Prix hors honoraires 350 000 €. Dans une copropriété de 65 lots. Quote-part moyenne du budget prévisionnel 1 228 €/an. Procédure en cours : 39/2173. Classe énergie C, Classe climat A. Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : https://www.georisques.gouv.fr.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 548 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 522 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="30">

--- a/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
+++ b/docs/dossiers/dossier-paris-16e-025aba2f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
